--- a/templates/Template_4_CoSchedule_Groups.xlsx
+++ b/templates/Template_4_CoSchedule_Groups.xlsx
@@ -17,19 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -44,23 +38,16 @@
     </font>
     <font>
       <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="00926B18"/>
-      <sz val="10"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="001B4965"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="002D6A4F"/>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -71,18 +58,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="001B4965"/>
         <bgColor rgb="001B4965"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E8F5EE"/>
-        <bgColor rgb="00E8F5EE"/>
       </patternFill>
     </fill>
   </fills>
@@ -112,16 +87,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -487,17 +460,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -559,79 +532,85 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>AP Art</t>
+          <t>Group Name</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>253, 254, 255, 764</t>
+          <t>Course Codes (comma separated)</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>AP Art courses share one period</t>
+          <t>Course Titles</t>
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr"/>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Period (if fixed)</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Semester</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Studio Art II-III</t>
+          <t xml:space="preserve">AP Art </t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>242, 243</t>
+          <t>253, 254, 255, 764</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Studio Art upper levels together</t>
+          <t>AP Art : AP Drawing, AP 2-D Art and Design, AP 3-D Art and Design</t>
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G5" s="4" t="n">
-        <v>3</v>
-      </c>
+      <c r="G5" s="4" t="inlineStr"/>
       <c r="H5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Robotics Project</t>
+          <t>Studio Art II-III</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>590, 591</t>
+          <t>242, 243</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Robotics paired sections</t>
+          <t>Studio Art II-III: Studio Art II, Studio Art III</t>
         </is>
       </c>
       <c r="D6" s="4" t="n">
@@ -647,7 +626,7 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr"/>
@@ -655,17 +634,17 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Italian III/AP</t>
+          <t>Robotics Project</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>333, 352</t>
+          <t>590, 591</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Italian upper levels co-scheduled</t>
+          <t>Robotics Project: Robotics Project, Robotics Project II</t>
         </is>
       </c>
       <c r="D7" s="4" t="n">
@@ -681,25 +660,29 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr"/>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Spring</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Guitar</t>
+          <t>Italian III/AP</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>201, 203</t>
+          <t>333, 352</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Guitar levels together</t>
+          <t>Italian III/AP: Italian III H, AP Italian</t>
         </is>
       </c>
       <c r="D8" s="4" t="n">
@@ -710,110 +693,81 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr"/>
-      <c r="H8" s="4" t="inlineStr"/>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Fall / Spring</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Theater</t>
+          <t>Guitar</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>227, 228</t>
+          <t>201, 203</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Theater levels together</t>
+          <t>Guitar: Introduction to Guitar, Guitar Ensemble</t>
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" s="4" t="n">
         <v>2</v>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr"/>
       <c r="H9" s="4" t="inlineStr"/>
     </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>HOW TO USE:</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>List groups of courses that MUST be scheduled in the same period.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Course Codes:</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>Comma-separated list of course codes that share a period (e.g., "253, 254, 255, 764")</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>Period:</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>Leave blank to let the engine choose, or enter A-G to fix the period</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>Semester:</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>Leave blank for engine choice, or enter S1/S2 to fix the semester</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>DELETE:</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>Delete the yellow example rows before uploading.</t>
-        </is>
-      </c>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Theater</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>227, 228</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Theater: Adv Theater Production</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B16:F16"/>
-    <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B13:F13"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/templates/Template_4_CoSchedule_Groups.xlsx
+++ b/templates/Template_4_CoSchedule_Groups.xlsx
@@ -1,127 +1,60 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jCiofalo\Desktop\AI MASTER SCHEDULER TEMPLATES 07.31.26\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D13C3900-E4E1-4E55-90F5-A542623863AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30168" windowHeight="19464" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="30168" windowHeight="19464" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Co-Schedule Groups" sheetId="1" r:id="rId1"/>
+    <sheet name="Co-Schedule Groups" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="19">
-  <si>
-    <t>Co-Schedule Group Name</t>
-  </si>
-  <si>
-    <t>Course Code</t>
-  </si>
-  <si>
-    <t>Teacher ID</t>
-  </si>
-  <si>
-    <t>Prescribed Room</t>
-  </si>
-  <si>
-    <t>REQUIRED</t>
-  </si>
-  <si>
-    <t>OPTIONAL</t>
-  </si>
-  <si>
-    <t>J-322</t>
-  </si>
-  <si>
-    <t>Theater Block</t>
-  </si>
-  <si>
-    <t>AP Art Block</t>
-  </si>
-  <si>
-    <t>Italian Block</t>
-  </si>
-  <si>
-    <t>Guitar Block</t>
-  </si>
-  <si>
-    <t>Studio Art Block</t>
-  </si>
-  <si>
-    <t>Programming Block</t>
-  </si>
-  <si>
-    <t>Robotics Block</t>
-  </si>
-  <si>
-    <t>S-237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">J-120 </t>
-  </si>
-  <si>
-    <t>Auditorium</t>
-  </si>
-  <si>
-    <t>J-223</t>
-  </si>
-  <si>
-    <t>S-338</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="5">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
     </font>
     <font>
-      <i/>
-      <sz val="10"/>
-      <color rgb="FF375623"/>
       <name val="Arial"/>
       <family val="2"/>
+      <i val="1"/>
+      <color rgb="FF375623"/>
+      <sz val="10"/>
     </font>
     <font>
-      <i/>
-      <sz val="10"/>
-      <color rgb="FF806000"/>
       <name val="Arial"/>
       <family val="2"/>
+      <i val="1"/>
+      <color rgb="FF806000"/>
+      <sz val="10"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="6">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -178,39 +111,98 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -498,266 +490,350 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D18"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14.44140625" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="28.2" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="4">
+    <row r="1" ht="28.2" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Co-Schedule Group Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Course Code</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Teacher ID</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Prescribed Room</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>REQUIRED</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>REQUIRED</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>REQUIRED</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>OPTIONAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>AP Art Block</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="n">
         <v>253</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3" s="5" t="n">
         <v>105810</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="4">
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>J-322</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>AP Art Block</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
         <v>254</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="5" t="n">
         <v>105810</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="4">
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>J-322</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>AP Art Block</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
         <v>255</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="5" t="n">
         <v>105810</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="4">
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>J-322</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>AP Art Block</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
         <v>764</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="5" t="n">
         <v>105810</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="6">
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>J-322</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Italian Block</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
         <v>333</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="5" t="n">
         <v>106762</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="6">
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>S-237</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Italian Block</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
         <v>359</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="5" t="n">
         <v>106762</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="6">
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>S-237</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Guitar Block</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
         <v>201</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9" s="5" t="n">
         <v>102255</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" s="6">
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>J-120</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Guitar Block</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
         <v>203</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10" s="5" t="n">
         <v>102255</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" s="6">
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>J-120</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Theater Block</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
         <v>227</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C11" s="5" t="n">
         <v>122002</v>
       </c>
-      <c r="D11" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B12" s="6">
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Auditorium</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Theater Block</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
         <v>228</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C12" s="5" t="n">
         <v>122002</v>
       </c>
-      <c r="D12" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13" s="6">
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Auditorium</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Studio Art Block</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
         <v>242</v>
       </c>
-      <c r="C13" s="5">
+      <c r="C13" s="5" t="n">
         <v>105810</v>
       </c>
-      <c r="D13" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B14" s="6">
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>J-322</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Studio Art Block</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
         <v>243</v>
       </c>
-      <c r="C14" s="5">
+      <c r="C14" s="5" t="n">
         <v>105810</v>
       </c>
-      <c r="D14" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B15" s="4">
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>J-322</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Programming Block</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
         <v>473</v>
       </c>
-      <c r="C15" s="5">
+      <c r="C15" s="5" t="n">
         <v>106753</v>
       </c>
-      <c r="D15" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B16" s="4">
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>J-223</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Programming Block</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
         <v>494</v>
       </c>
-      <c r="C16" s="5">
+      <c r="C16" s="5" t="n">
         <v>106753</v>
       </c>
-      <c r="D16" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B17" s="4">
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>J-223</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Robotics Block</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
         <v>590</v>
       </c>
-      <c r="C17" s="5">
+      <c r="C17" s="5" t="n">
         <v>117304</v>
       </c>
-      <c r="D17" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B18" s="4">
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>S-338</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Robotics Block</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
         <v>591</v>
       </c>
-      <c r="C18" s="5">
+      <c r="C18" s="5" t="n">
         <v>117304</v>
       </c>
-      <c r="D18" s="4" t="s">
-        <v>18</v>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>S-338</t>
+        </is>
       </c>
     </row>
   </sheetData>
